--- a/data-manipulation-scripts/sheets-cleanup/sheets/COROA - 29_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/COROA - 29_01.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -28,19 +28,22 @@
     <t>7899468082160</t>
   </si>
   <si>
-    <t>COROA FC TRILHA YES125 2004 A 2016</t>
+    <t>COROA FIXACAO CUBO  TRILHA YES125 2004 A 2016</t>
   </si>
   <si>
     <t>7908073743301</t>
   </si>
   <si>
-    <t>COROA FC SMARTFOX YBR125 2000 A 2008/ CRYPTON105</t>
+    <t>COROA FIXACAO CUBO  SMARTFOX YBR125 2000 A 2008/ CRYPTON105</t>
   </si>
   <si>
     <t>070341176641</t>
   </si>
   <si>
-    <t>COROA FC IRON SHINERAY XY50 118970</t>
+    <t>COROA FIXACAO CUBO  IRON SHINERAY XY50 118970</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -391,7 +394,9 @@
       <c r="D6" s="4"/>
     </row>
     <row r="7">
-      <c r="A7" s="3"/>
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
